--- a/data/guitar_catalog.xlsx
+++ b/data/guitar_catalog.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\prasjosh\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://capgemini-my.sharepoint.com/personal/prasad_a_joshi_capgemini_com2/Documents/CG Work/guitar-agents-lab/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74AA5D91-0084-4F0E-951A-01057E423DEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{74AA5D91-0084-4F0E-951A-01057E423DEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E88857DE-3371-4EEB-8DE5-D3BEEB7196C3}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$M$181</definedName>
+  </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
@@ -956,6 +959,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1248,6 +1255,7 @@
   <dimension ref="A1:M181"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
+    <col min="2" max="2" width="17.1796875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="15.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
